--- a/absalon/Deltagerliste uge 34.xlsx
+++ b/absalon/Deltagerliste uge 34.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zfp165/Documents/DIKU TEACHING/24_kicker_p5/absalon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1845F5B3-0074-6E45-96A8-9FADADA1CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC320D12-B38A-9344-AEF6-340D4D5173C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="23500" xr2:uid="{C8E17647-27B4-5042-B454-DC148F83902B}"/>
+    <workbookView xWindow="6300" yWindow="4160" windowWidth="38400" windowHeight="23500" xr2:uid="{C8E17647-27B4-5042-B454-DC148F83902B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="277">
   <si>
     <t>Fornavn</t>
   </si>
@@ -854,9 +854,6 @@
   </si>
   <si>
     <t>ALPHA</t>
-  </si>
-  <si>
-    <t>BETA</t>
   </si>
   <si>
     <t>CHARLIE</t>
@@ -933,7 +930,7 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -951,7 +948,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -981,8 +978,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}" name="Table1" displayName="Table1" ref="A1:E98" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:E98" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}" name="Table1" displayName="Table1" ref="A1:E98" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:E98" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="BETA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E95">
     <sortCondition ref="A1:A98"/>
   </sortState>
@@ -991,7 +994,7 @@
     <tableColumn id="2" xr3:uid="{0C6012B0-4ED4-F045-9F29-3028D637CDF1}" name="Efternavn"/>
     <tableColumn id="3" xr3:uid="{02B62585-1D35-8944-88BB-9EC92615E012}" name="E-mail"/>
     <tableColumn id="4" xr3:uid="{C606D4E3-4704-D74B-A7E5-BC04F60F30CB}" name="Vælg din uddannelse"/>
-    <tableColumn id="5" xr3:uid="{7A5D8F61-2763-8F47-9FD6-DB61B5573E84}" name="Group" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{7A5D8F61-2763-8F47-9FD6-DB61B5573E84}" name="Group" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1342,7 +1345,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1373,10 +1376,10 @@
         <v>129</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1390,10 +1393,10 @@
         <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1407,10 +1410,10 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>213</v>
       </c>
@@ -1441,10 +1444,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1458,10 +1461,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1475,7 +1478,7 @@
         <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
@@ -1492,10 +1495,10 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -1509,10 +1512,10 @@
         <v>129</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>240</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1543,10 +1546,10 @@
         <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1577,10 +1580,10 @@
         <v>129</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1594,10 +1597,10 @@
         <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>173</v>
       </c>
@@ -1611,10 +1614,10 @@
         <v>129</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -1645,10 +1648,10 @@
         <v>203</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>166</v>
       </c>
@@ -1662,10 +1665,10 @@
         <v>129</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1679,10 +1682,10 @@
         <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>207</v>
       </c>
@@ -1713,10 +1716,10 @@
         <v>129</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>216</v>
       </c>
@@ -1730,10 +1733,10 @@
         <v>203</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -1747,10 +1750,10 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>169</v>
       </c>
@@ -1781,10 +1784,10 @@
         <v>7</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -1798,10 +1801,10 @@
         <v>129</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -1815,10 +1818,10 @@
         <v>7</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -1832,10 +1835,10 @@
         <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -1866,10 +1869,10 @@
         <v>225</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1883,10 +1886,10 @@
         <v>7</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>231</v>
       </c>
@@ -1917,10 +1920,10 @@
         <v>203</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>92</v>
       </c>
@@ -1934,10 +1937,10 @@
         <v>225</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -1951,10 +1954,10 @@
         <v>7</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>106</v>
       </c>
@@ -1968,10 +1971,10 @@
         <v>7</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -2002,10 +2005,10 @@
         <v>129</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>234</v>
       </c>
@@ -2019,10 +2022,10 @@
         <v>225</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>268</v>
       </c>
@@ -2053,10 +2056,10 @@
         <v>225</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -2070,10 +2073,10 @@
         <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -2087,10 +2090,10 @@
         <v>7</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2121,10 +2124,10 @@
         <v>225</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -2138,10 +2141,10 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>136</v>
       </c>
@@ -2155,10 +2158,10 @@
         <v>129</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -2189,10 +2192,10 @@
         <v>225</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>133</v>
       </c>
@@ -2206,10 +2209,10 @@
         <v>129</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>258</v>
       </c>
@@ -2226,7 +2229,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>151</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>129</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
@@ -2257,10 +2260,10 @@
         <v>129</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>7</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
@@ -2291,10 +2294,10 @@
         <v>7</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>163</v>
       </c>
@@ -2308,10 +2311,10 @@
         <v>129</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -2325,10 +2328,10 @@
         <v>7</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>139</v>
       </c>
@@ -2359,10 +2362,10 @@
         <v>225</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>197</v>
       </c>
@@ -2376,10 +2379,10 @@
         <v>129</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -2393,7 +2396,7 @@
         <v>129</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
@@ -2410,10 +2413,10 @@
         <v>129</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>53</v>
       </c>
@@ -2444,10 +2447,10 @@
         <v>7</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>84</v>
       </c>
@@ -2461,10 +2464,10 @@
         <v>7</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -2478,10 +2481,10 @@
         <v>129</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>182</v>
       </c>
@@ -2512,10 +2515,10 @@
         <v>129</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>157</v>
       </c>
@@ -2529,10 +2532,10 @@
         <v>129</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>200</v>
       </c>
@@ -2546,10 +2549,10 @@
         <v>203</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>222</v>
       </c>
@@ -2563,10 +2566,10 @@
         <v>225</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -2583,7 +2586,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>203</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
@@ -2614,10 +2617,10 @@
         <v>129</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>72</v>
       </c>
@@ -2634,7 +2637,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>204</v>
       </c>
@@ -2648,7 +2651,7 @@
         <v>203</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
@@ -2665,10 +2668,10 @@
         <v>7</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>59</v>
       </c>
@@ -2682,10 +2685,10 @@
         <v>7</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>223</v>
       </c>
@@ -2699,10 +2702,10 @@
         <v>225</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>228</v>
       </c>
@@ -2716,10 +2719,10 @@
         <v>225</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -2736,7 +2739,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>263</v>
       </c>
@@ -2750,7 +2753,7 @@
         <v>225</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
@@ -2767,10 +2770,10 @@
         <v>7</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -2801,10 +2804,10 @@
         <v>7</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>23</v>
       </c>
@@ -2818,10 +2821,10 @@
         <v>7</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2835,7 +2838,7 @@
         <v>225</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
@@ -2852,10 +2855,10 @@
         <v>7</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>246</v>
       </c>
@@ -2869,10 +2872,10 @@
         <v>225</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>255</v>
       </c>
@@ -2886,10 +2889,10 @@
         <v>225</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -2920,10 +2923,10 @@
         <v>7</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>62</v>
       </c>
@@ -2937,10 +2940,10 @@
         <v>7</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>118</v>
       </c>
@@ -2954,10 +2957,10 @@
         <v>225</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>62</v>
       </c>
@@ -2988,7 +2991,7 @@
         <v>7</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3021,7 +3024,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -3043,7 +3046,7 @@
         <v>180</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -3063,7 +3066,7 @@
         <v>60</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
@@ -3083,7 +3086,7 @@
         <v>30</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -3103,7 +3106,7 @@
         <v>143</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
@@ -3123,7 +3126,7 @@
         <v>211</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
@@ -3143,7 +3146,7 @@
         <v>155</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
@@ -3163,7 +3166,7 @@
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
@@ -3183,7 +3186,7 @@
         <v>137</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
@@ -3203,7 +3206,7 @@
         <v>220</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
@@ -3223,7 +3226,7 @@
         <v>195</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
@@ -3243,7 +3246,7 @@
         <v>261</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
@@ -3263,7 +3266,7 @@
         <v>244</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
@@ -3283,7 +3286,7 @@
         <v>238</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
@@ -3303,7 +3306,7 @@
         <v>161</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
@@ -3323,7 +3326,7 @@
         <v>66</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
@@ -3343,7 +3346,7 @@
         <v>251</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
@@ -3363,7 +3366,7 @@
         <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
@@ -3383,7 +3386,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
@@ -3403,7 +3406,7 @@
         <v>172</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
@@ -3423,7 +3426,7 @@
         <v>186</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
@@ -3443,7 +3446,7 @@
         <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
@@ -3463,7 +3466,7 @@
         <v>57</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
@@ -3483,7 +3486,7 @@
         <v>122</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
@@ -3503,7 +3506,7 @@
         <v>113</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
@@ -3514,18 +3517,18 @@
         <v>45</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="23" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
@@ -3536,7 +3539,7 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E29" t="s">
         <v>14</v>
@@ -3545,7 +3548,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
@@ -3556,7 +3559,7 @@
         <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -3565,7 +3568,7 @@
         <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
@@ -3576,7 +3579,7 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
@@ -3585,7 +3588,7 @@
         <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
@@ -3596,7 +3599,7 @@
         <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E32" t="s">
         <v>47</v>
@@ -3605,7 +3608,7 @@
         <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
@@ -3616,7 +3619,7 @@
         <v>167</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E33" t="s">
         <v>4</v>
@@ -3625,7 +3628,7 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
@@ -3636,7 +3639,7 @@
         <v>217</v>
       </c>
       <c r="C34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E34" t="s">
         <v>56</v>
@@ -3645,7 +3648,7 @@
         <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
@@ -3656,7 +3659,7 @@
         <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E35" t="s">
         <v>81</v>
@@ -3665,7 +3668,7 @@
         <v>82</v>
       </c>
       <c r="G35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
@@ -3676,7 +3679,7 @@
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
         <v>92</v>
@@ -3685,7 +3688,7 @@
         <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
@@ -3696,7 +3699,7 @@
         <v>253</v>
       </c>
       <c r="C37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E37" t="s">
         <v>103</v>
@@ -3705,7 +3708,7 @@
         <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
@@ -3716,7 +3719,7 @@
         <v>235</v>
       </c>
       <c r="C38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E38" t="s">
         <v>106</v>
@@ -3725,7 +3728,7 @@
         <v>107</v>
       </c>
       <c r="G38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
@@ -3736,7 +3739,7 @@
         <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E39" t="s">
         <v>87</v>
@@ -3745,7 +3748,7 @@
         <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
@@ -3756,7 +3759,7 @@
         <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E40" t="s">
         <v>136</v>
@@ -3765,7 +3768,7 @@
         <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
@@ -3776,7 +3779,7 @@
         <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E41" t="s">
         <v>151</v>
@@ -3785,7 +3788,7 @@
         <v>152</v>
       </c>
       <c r="G41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
@@ -3796,7 +3799,7 @@
         <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E42" t="s">
         <v>163</v>
@@ -3805,7 +3808,7 @@
         <v>164</v>
       </c>
       <c r="G42" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
@@ -3816,7 +3819,7 @@
         <v>101</v>
       </c>
       <c r="C43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E43" t="s">
         <v>176</v>
@@ -3825,7 +3828,7 @@
         <v>177</v>
       </c>
       <c r="G43" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
@@ -3836,7 +3839,7 @@
         <v>198</v>
       </c>
       <c r="C44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E44" t="s">
         <v>87</v>
@@ -3845,7 +3848,7 @@
         <v>189</v>
       </c>
       <c r="G44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
@@ -3856,7 +3859,7 @@
         <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E45" t="s">
         <v>200</v>
@@ -3865,7 +3868,7 @@
         <v>201</v>
       </c>
       <c r="G45" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
@@ -3876,7 +3879,7 @@
         <v>158</v>
       </c>
       <c r="C46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E46" t="s">
         <v>84</v>
@@ -3885,7 +3888,7 @@
         <v>209</v>
       </c>
       <c r="G46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
@@ -3896,7 +3899,7 @@
         <v>223</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E47" t="s">
         <v>223</v>
@@ -3905,7 +3908,7 @@
         <v>226</v>
       </c>
       <c r="G47" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
@@ -3916,7 +3919,7 @@
         <v>205</v>
       </c>
       <c r="C48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E48" t="s">
         <v>228</v>
@@ -3925,7 +3928,7 @@
         <v>229</v>
       </c>
       <c r="G48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
@@ -3936,7 +3939,7 @@
         <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E49" t="s">
         <v>4</v>
@@ -3945,7 +3948,7 @@
         <v>137</v>
       </c>
       <c r="G49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
@@ -3956,7 +3959,7 @@
         <v>264</v>
       </c>
       <c r="C50" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E50" t="s">
         <v>255</v>
@@ -3965,7 +3968,7 @@
         <v>256</v>
       </c>
       <c r="G50" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
@@ -3976,7 +3979,7 @@
         <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E51" t="s">
         <v>118</v>
@@ -3985,7 +3988,7 @@
         <v>266</v>
       </c>
       <c r="G51" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
@@ -3996,7 +3999,7 @@
         <v>247</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E52" t="s">
         <v>62</v>
@@ -4005,7 +4008,7 @@
         <v>124</v>
       </c>
       <c r="G52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/absalon/Deltagerliste uge 34.xlsx
+++ b/absalon/Deltagerliste uge 34.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zfp165/Documents/DIKU TEACHING/24_kicker_p5/absalon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC320D12-B38A-9344-AEF6-340D4D5173C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F463A8A-E688-B847-91D0-362D9EBE8769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="4160" windowWidth="38400" windowHeight="23500" xr2:uid="{C8E17647-27B4-5042-B454-DC148F83902B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="23500" xr2:uid="{C8E17647-27B4-5042-B454-DC148F83902B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
@@ -980,9 +982,15 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}" name="Table1" displayName="Table1" ref="A1:E98" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:E98" xr:uid="{6082EF77-4005-524F-8EA5-80AA32E78505}">
-    <filterColumn colId="4">
+    <filterColumn colId="0">
       <filters>
-        <filter val="BETA"/>
+        <filter val="Agnes Wenzel"/>
+        <filter val="Andreas"/>
+        <filter val="Carl"/>
+        <filter val="Janus Aleksander Kleve"/>
+        <filter val="Jonas"/>
+        <filter val="Jora"/>
+        <filter val="Thomas"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1345,7 +1353,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1362,7 +1370,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>179</v>
       </c>
@@ -1379,7 +1387,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>90</v>
       </c>
@@ -1481,7 +1489,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1498,7 +1506,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -1566,7 +1574,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>142</v>
       </c>
@@ -1634,7 +1642,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>142</v>
       </c>
@@ -1770,7 +1778,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -1855,7 +1863,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>270</v>
       </c>
@@ -1872,7 +1880,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -1906,7 +1914,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>219</v>
       </c>
@@ -1923,7 +1931,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>92</v>
       </c>
@@ -1991,7 +1999,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>194</v>
       </c>
@@ -2042,7 +2050,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>260</v>
       </c>
@@ -2110,7 +2118,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>243</v>
       </c>
@@ -2246,7 +2254,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>160</v>
       </c>
@@ -2280,7 +2288,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -2297,7 +2305,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>163</v>
       </c>
@@ -2348,7 +2356,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -2399,7 +2407,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>130</v>
       </c>
@@ -2433,7 +2441,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -2501,7 +2509,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -2603,7 +2611,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>185</v>
       </c>
@@ -2654,7 +2662,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -2756,7 +2764,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>56</v>
       </c>
@@ -2790,7 +2798,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>121</v>
       </c>
@@ -2841,7 +2849,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>112</v>
       </c>
@@ -2858,7 +2866,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>246</v>
       </c>
@@ -2909,7 +2917,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>44</v>
       </c>
@@ -2977,7 +2985,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>98</v>
       </c>
